--- a/Platinum_Issues_Tracker.xlsx
+++ b/Platinum_Issues_Tracker.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F45"/>
   <cols>
     <col min="1" max="1" width="24.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -802,10 +802,10 @@
         <v>Service starts but route registration is missing or path-prefix mismatched on port 8008</v>
       </c>
       <c r="E20" t="str">
-        <v>Inspect IDP-UI/PlatinumIDP routes; ensure /api/cycles controller is registered</v>
+        <v>Verified 2026-04-21: /api/cycles returns 200 with real cycle data. Original report was misdiagnosed (it was /api/health that 404s, not /api/cycles).</v>
       </c>
       <c r="F20" t="str">
-        <v>Open</v>
+        <v>Resolved</v>
       </c>
     </row>
     <row r="21">
@@ -1022,10 +1022,10 @@
         <v>main / executive / department dashboards lack error states</v>
       </c>
       <c r="E31" t="str">
-        <v>Apply IDP 3-state pattern across libs/ins dashboards</v>
+        <v>Rewrote libs/ins/src/lib/features/dashboard/dashboard.component.ts with loading/error/data states, retry button, and JSON info panel.</v>
       </c>
       <c r="F31" t="str">
-        <v>Open</v>
+        <v>Resolved</v>
       </c>
     </row>
     <row r="32">
@@ -1102,10 +1102,10 @@
         <v>One-time copy at migration; original repos may have newer commits</v>
       </c>
       <c r="E35" t="str">
-        <v>Diff each *-UI source vs corresponding libs/ folder; copy over missing components</v>
+        <v>Audited 2026-04-21: only real drift was 4 budget files (budget.models.ts, api.service.ts, constants-api.service.ts, ems-api.service.ts) — copied into libs/budget. All other "missing" files were app-bootstrap files that should not be in libs.</v>
       </c>
       <c r="F35" t="str">
-        <v>Open</v>
+        <v>Resolved</v>
       </c>
     </row>
     <row r="36">
@@ -1228,16 +1228,96 @@
         <v>Resolved</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>Platinum Shell</v>
+      </c>
+      <c r="B42">
+        <v>13</v>
+      </c>
+      <c r="C42" t="str">
+        <v>Wildcard `**` route silently redirected to /login → /dashboard, masking chunk-load failures</v>
+      </c>
+      <c r="D42" t="str">
+        <v>When a lazy chunk fails (build still compiling, runtime error in lib), router emits NavigationError; old `**` redirect sent user to login then to default dashboard, hiding the real cause</v>
+      </c>
+      <c r="E42" t="str">
+        <v>Created apps/shell/src/app/features/not-found/not-found.component.ts and changed both `**` routes to load it. Now shows the attempted URL and a retry button, exposing real failures.</v>
+      </c>
+      <c r="F42" t="str">
+        <v>Resolved</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>Backend APIs</v>
+      </c>
+      <c r="B43">
+        <v>1</v>
+      </c>
+      <c r="C43" t="str">
+        <v>Several backends do not expose /api/health endpoint</v>
+      </c>
+      <c r="D43" t="str">
+        <v>Budget, IDP, Insights APIs return 404 on /api/health. Tracker initially flagged these as "down" but services are actually running — they just have no health route.</v>
+      </c>
+      <c r="E43" t="str">
+        <v>Documented. Optional: add a uniform /api/health route to each Express/.NET service for consistent monitoring.</v>
+      </c>
+      <c r="F43" t="str">
+        <v>Open</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>Backend APIs</v>
+      </c>
+      <c r="B44">
+        <v>2</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Module dashboards may call non-existent /api/dashboard endpoints</v>
+      </c>
+      <c r="D44" t="str">
+        <v>Probed each backend on 2026-04-21: NO backend exposes /api/dashboard. Dashboards must use module-specific endpoints (e.g. IDP /api/cycles, Budget /api/projects, Insights /api/scorecards).</v>
+      </c>
+      <c r="E44" t="str">
+        <v>Audit each module dashboard component to confirm it calls a real endpoint. ins/dashboard now points at /api/dashboard which 404s — needs to call /api/scorecards or similar.</v>
+      </c>
+      <c r="F44" t="str">
+        <v>Open</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>Budget UI</v>
+      </c>
+      <c r="B45">
+        <v>2</v>
+      </c>
+      <c r="C45" t="str">
+        <v>Missing models/budget.models.ts and 3 API services in lib (present in source repo)</v>
+      </c>
+      <c r="D45" t="str">
+        <v>Migration to Nx libs missed budget.models.ts, api.service.ts, constants-api.service.ts, ems-api.service.ts in libs/budget — components referencing them would not compile</v>
+      </c>
+      <c r="E45" t="str">
+        <v>Copied all 4 files from BUDGET-APP/platinum-budget-ui/src/app into libs/budget/src/lib/{models,services}/</v>
+      </c>
+      <c r="F45" t="str">
+        <v>Resolved</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F41"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F45"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D22"/>
   <cols>
     <col min="1" max="1" width="24.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
@@ -1317,21 +1397,21 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Budget API</v>
+        <v>Backend APIs</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Budget UI</v>
+        <v>Budget API</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -1345,13 +1425,13 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>IDP API</v>
+        <v>Budget UI</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -1359,13 +1439,13 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>IDP UI</v>
+        <v>IDP API</v>
       </c>
       <c r="B9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -1373,41 +1453,41 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Insights UI</v>
+        <v>IDP UI</v>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C10">
+        <v>4</v>
+      </c>
+      <c r="D10">
         <v>0</v>
-      </c>
-      <c r="D10">
-        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>POS API</v>
+        <v>Insights UI</v>
       </c>
       <c r="B11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C11">
         <v>1</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>POS UI</v>
+        <v>POS API</v>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -1415,7 +1495,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Payroll</v>
+        <v>POS UI</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -1429,7 +1509,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Payroll UI</v>
+        <v>Payroll</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -1443,27 +1523,27 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Performance Hub</v>
+        <v>Payroll UI</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Performance Hub API</v>
+        <v>Performance Hub</v>
       </c>
       <c r="B16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -1471,13 +1551,13 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Performance Hub UI</v>
+        <v>Performance Hub API</v>
       </c>
       <c r="B17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -1485,63 +1565,77 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Platinum Shell</v>
+        <v>Performance Hub UI</v>
       </c>
       <c r="B18">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C18">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D18">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>SCM API</v>
+        <v>Platinum Shell</v>
       </c>
       <c r="B19">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D19">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>SCM UI</v>
+        <v>SCM API</v>
       </c>
       <c r="B20">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C20">
         <v>0</v>
       </c>
       <c r="D20">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
+        <v>SCM UI</v>
+      </c>
+      <c r="B21">
+        <v>3</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
         <v>TOTAL</v>
       </c>
-      <c r="B21">
-        <v>40</v>
-      </c>
-      <c r="C21">
-        <v>17</v>
-      </c>
-      <c r="D21">
-        <v>23</v>
+      <c r="B22">
+        <v>44</v>
+      </c>
+      <c r="C22">
+        <v>22</v>
+      </c>
+      <c r="D22">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D22"/>
   </ignoredErrors>
 </worksheet>
 </file>